--- a/artfynd/A 57758-2025 artfynd.xlsx
+++ b/artfynd/A 57758-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820468</v>
+        <v>121150732</v>
       </c>
       <c r="B2" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>728406</v>
+        <v>728365</v>
       </c>
       <c r="R2" t="n">
-        <v>7209797</v>
+        <v>7209832</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -789,16 +784,11 @@
         <v>121150731</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150732</v>
+        <v>119820468</v>
       </c>
       <c r="B4" t="n">
-        <v>91983</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>728365</v>
+        <v>728406</v>
       </c>
       <c r="R4" t="n">
-        <v>7209832</v>
+        <v>7209797</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
